--- a/experiments/manifests/m3_pairs_draft.xlsx
+++ b/experiments/manifests/m3_pairs_draft.xlsx
@@ -8348,12 +8348,12 @@
       <c r="O94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>T2</t>
         </is>
       </c>
       <c r="Q94" t="inlineStr">
         <is>
-          <t>검수: 'located'가 지리적 의미 — 같은 블록이면 T2로 adjudication</t>
+          <t>검수(2차): 두 질문 모두 'NASHVILLE, TENNESSEE' 같은 블록 참조 — T2 타당, adjudication 확정 요망</t>
         </is>
       </c>
       <c r="R94" t="b">
